--- a/excel/SmartTrader_ERP_C.xlsx
+++ b/excel/SmartTrader_ERP_C.xlsx
@@ -238,7 +238,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -371,6 +371,12 @@
         <bgColor rgb="005E35B1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -411,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -655,6 +661,24 @@
     </xf>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3397,14 +3421,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3745,6 +3769,130 @@
       <c r="B28" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">     entered beyond the Free limit were kept and are counted the moment Pro is active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="123" t="inlineStr">
+        <is>
+          <t>HOW PRO COMPARES (yearly price, Oct 2026 listings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="126" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C31" s="127" t="inlineStr">
+        <is>
+          <t>Price / year</t>
+        </is>
+      </c>
+      <c r="D31" s="127" t="inlineStr">
+        <is>
+          <t>Per month</t>
+        </is>
+      </c>
+      <c r="E31" s="126" t="inlineStr">
+        <is>
+          <t>Works offline, your data stays in your file</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="128" t="inlineStr">
+        <is>
+          <t>SmartTrader Pro (this file)</t>
+        </is>
+      </c>
+      <c r="C32" s="129" t="inlineStr">
+        <is>
+          <t>Rs 1,299</t>
+        </is>
+      </c>
+      <c r="D32" s="129" t="inlineStr">
+        <is>
+          <t>Rs 108</t>
+        </is>
+      </c>
+      <c r="E32" s="128" t="inlineStr">
+        <is>
+          <t>Yes - plain Excel, no login</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="130" t="inlineStr">
+        <is>
+          <t>myBillBook Plus / Pro</t>
+        </is>
+      </c>
+      <c r="C33" s="131" t="inlineStr">
+        <is>
+          <t>Rs 3,490 - 3,990</t>
+        </is>
+      </c>
+      <c r="D33" s="131" t="inlineStr">
+        <is>
+          <t>Rs 291 - 333</t>
+        </is>
+      </c>
+      <c r="E33" s="130" t="inlineStr">
+        <is>
+          <t>Cloud account</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="130" t="inlineStr">
+        <is>
+          <t>Vyapar Desktop</t>
+        </is>
+      </c>
+      <c r="C34" s="131" t="inlineStr">
+        <is>
+          <t>Rs 3,399 - 4,099</t>
+        </is>
+      </c>
+      <c r="D34" s="131" t="inlineStr">
+        <is>
+          <t>Rs 283 - 342</t>
+        </is>
+      </c>
+      <c r="E34" s="130" t="inlineStr">
+        <is>
+          <t>Desktop app</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="130" t="inlineStr">
+        <is>
+          <t>TallyPrime Silver (rental)</t>
+        </is>
+      </c>
+      <c r="C35" s="131" t="inlineStr">
+        <is>
+          <t>Rs 8,100</t>
+        </is>
+      </c>
+      <c r="D35" s="131" t="inlineStr">
+        <is>
+          <t>Rs 675</t>
+        </is>
+      </c>
+      <c r="E35" s="130" t="inlineStr">
+        <is>
+          <t>Desktop app</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Competitor prices are public listings and change often; they include cloud/mobile features this file does not.</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3943,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="126" t="inlineStr">
+      <c r="B4" s="132" t="inlineStr">
         <is>
           <t>DAILY FLOW: PROCURE → STOCK → SELL → DELIVER → COLLECT</t>
         </is>
@@ -3803,103 +3951,103 @@
       <c r="C4" s="57" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="127" t="inlineStr">
+      <c r="B5" s="133" t="inlineStr">
         <is>
           <t>1. Set up once</t>
         </is>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="134" t="inlineStr">
         <is>
           <t>Settings: company, GSTIN, home state, FY start, opening cash/bank. Items: product list with opening stock. Parties: customers &amp; suppliers with state and credit limit.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="127" t="inlineStr">
+      <c r="B6" s="133" t="inlineStr">
         <is>
           <t>2. Buy (Purchases)</t>
         </is>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="134" t="inlineStr">
         <is>
           <t>Pick supplier and item from dropdowns, type qty. Rate blank = standard purchase rate. 'Paid Via' blank = on credit (creates payable).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="127" t="inlineStr">
+      <c r="B7" s="133" t="inlineStr">
         <is>
           <t>3. Stock updates itself</t>
         </is>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="134" t="inlineStr">
         <is>
           <t>Items sheet instantly shows closing stock, weighted-average cost, stock value and REORDER / OUT OF STOCK / DEAD STOCK alerts.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="127" t="inlineStr">
+      <c r="B8" s="133" t="inlineStr">
         <is>
           <t>4. Sell (Sales)</t>
         </is>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="134" t="inlineStr">
         <is>
           <t>One line per item; keep all lines of an invoice together. CGST+SGST or IGST is chosen automatically from customer state vs. your home state. 'Stock Check' warns on negative stock or selling below cost.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="B9" s="127" t="inlineStr">
+      <c r="B9" s="133" t="inlineStr">
         <is>
           <t>5. Print invoice</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="134" t="inlineStr">
         <is>
           <t>Invoice sheet shows the latest invoice automatically. Type any invoice number in the cream cell to reprint. Ctrl+P (fits one A4 page). Doubles as delivery challan.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="B10" s="127" t="inlineStr">
+      <c r="B10" s="133" t="inlineStr">
         <is>
           <t>6. Deliver</t>
         </is>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="134" t="inlineStr">
         <is>
           <t>Set the Delivery column (Pending / Packed / Dispatched / Delivered). Dashboard counts what is still pending.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="127" t="inlineStr">
+      <c r="B11" s="133" t="inlineStr">
         <is>
           <t>7. Collect &amp; pay (CashBook)</t>
         </is>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="134" t="inlineStr">
         <is>
           <t>Receipt = money from customer; Payment = money to supplier; Expense = shop costs; Transfer In/Out moves money between Cash/Bank/UPI (enter both legs).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="B12" s="127" t="inlineStr">
+      <c r="B12" s="133" t="inlineStr">
         <is>
           <t>8. Review</t>
         </is>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="134" t="inlineStr">
         <is>
           <t>Dashboard for the live picture, Reports for monthly P&amp;L, GST rate-wise summary and expense analysis.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="126" t="inlineStr">
+      <c r="B14" s="132" t="inlineStr">
         <is>
           <t>PAIN POINTS THIS SOLVES</t>
         </is>
@@ -3907,103 +4055,103 @@
       <c r="C14" s="57" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="127" t="inlineStr">
+      <c r="B15" s="133" t="inlineStr">
         <is>
           <t>Stock never matches</t>
         </is>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="134" t="inlineStr">
         <is>
           <t>Single source of truth: stock = opening + purchases − sales ± adjustments. No manual stock register.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="B16" s="127" t="inlineStr">
+      <c r="B16" s="133" t="inlineStr">
         <is>
           <t>Don't know real profit</t>
         </is>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="134" t="inlineStr">
         <is>
           <t>Every sale line carries COGS at weighted-average cost, so gross and net profit are exact per line, item, month.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="B17" s="127" t="inlineStr">
+      <c r="B17" s="133" t="inlineStr">
         <is>
           <t>Money stuck with customers</t>
         </is>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="134" t="inlineStr">
         <is>
           <t>Party ledger with credit limit, credit days, OVERDUE / OVER LIMIT flags and Days Unpaid.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="127" t="inlineStr">
+      <c r="B18" s="133" t="inlineStr">
         <is>
           <t>Running out / overstock</t>
         </is>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="134" t="inlineStr">
         <is>
           <t>Reorder level + suggested order qty, days-of-cover, and dead-stock detection (no sale in N days).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="127" t="inlineStr">
+      <c r="B19" s="133" t="inlineStr">
         <is>
           <t>GST headache</t>
         </is>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="134" t="inlineStr">
         <is>
           <t>Automatic CGST/SGST vs IGST split, rate-wise output vs input summary per FY, net payable on dashboard.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="127" t="inlineStr">
+      <c r="B20" s="133" t="inlineStr">
         <is>
           <t>Double entry for cash sales</t>
         </is>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="134" t="inlineStr">
         <is>
           <t>'Paid Via' on the bill itself books cash/bank/UPI immediately - no separate receipt needed.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="127" t="inlineStr">
+      <c r="B21" s="133" t="inlineStr">
         <is>
           <t>Typing errors</t>
         </is>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="134" t="inlineStr">
         <is>
           <t>Dropdowns everywhere, unique-name checks, qty/date validation, row-level 'Check' columns.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="127" t="inlineStr">
+      <c r="B22" s="133" t="inlineStr">
         <is>
           <t>Slow, crashing Excel files</t>
         </is>
       </c>
-      <c r="C22" s="128" t="inlineStr">
+      <c r="C22" s="134" t="inlineStr">
         <is>
           <t>See SPEED DESIGN below.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="126" t="inlineStr">
+      <c r="B24" s="132" t="inlineStr">
         <is>
           <t>SPEED DESIGN (why it stays fast)</t>
         </is>
@@ -4011,67 +4159,67 @@
       <c r="C24" s="57" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="B25" s="127" t="inlineStr">
+      <c r="B25" s="133" t="inlineStr">
         <is>
           <t>No volatile functions</t>
         </is>
       </c>
-      <c r="C25" s="128" t="inlineStr">
+      <c r="C25" s="134" t="inlineStr">
         <is>
           <t>No OFFSET/INDIRECT in cell formulas; TODAY() appears once (Settings!B10). Volatile names are used only by dropdowns, which are not recalculated.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="127" t="inlineStr">
+      <c r="B26" s="133" t="inlineStr">
         <is>
           <t>Bounded ranges</t>
         </is>
       </c>
-      <c r="C26" s="128" t="inlineStr">
+      <c r="C26" s="134" t="inlineStr">
         <is>
           <t>All lookups use fixed ranges (20,000 transaction rows, 2000 items, 1000 parties) - never whole-column A:A references.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="B27" s="127" t="inlineStr">
+      <c r="B27" s="133" t="inlineStr">
         <is>
           <t>Match once, reuse</t>
         </is>
       </c>
-      <c r="C27" s="128" t="inlineStr">
+      <c r="C27" s="134" t="inlineStr">
         <is>
           <t>Each transaction row runs one MATCH into a hidden helper column, then several cheap INDEX calls reuse it.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="B28" s="127" t="inlineStr">
+      <c r="B28" s="133" t="inlineStr">
         <is>
           <t>SUMIFS engine</t>
         </is>
       </c>
-      <c r="C28" s="128" t="inlineStr">
+      <c r="C28" s="134" t="inlineStr">
         <is>
           <t>All aggregation uses SUMIFS/COUNTIFS - Excel's fastest multi-threaded aggregation functions. No SUMPRODUCT or array formulas.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="B29" s="127" t="inlineStr">
+      <c r="B29" s="133" t="inlineStr">
         <is>
           <t>Extra boost (optional)</t>
         </is>
       </c>
-      <c r="C29" s="128" t="inlineStr">
+      <c r="C29" s="134" t="inlineStr">
         <is>
           <t>Import ERP_Macros.bas (File &gt; Save As .xlsm, Alt+F11 &gt; File &gt; Import) for one-click Fast Mode, new invoice, PDF invoice, backup and archive.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="126" t="inlineStr">
+      <c r="B31" s="132" t="inlineStr">
         <is>
           <t>RULES &amp; LIMITS</t>
         </is>
@@ -4079,79 +4227,79 @@
       <c r="C31" s="57" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="127" t="inlineStr">
+      <c r="B32" s="133" t="inlineStr">
         <is>
           <t>Colour code</t>
         </is>
       </c>
-      <c r="C32" s="128" t="inlineStr">
+      <c r="C32" s="134" t="inlineStr">
         <is>
           <t>Blue text on cream = you type. Black/grey = formula, never overwrite. Green = linked from another sheet.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="B33" s="127" t="inlineStr">
+      <c r="B33" s="133" t="inlineStr">
         <is>
           <t>Sample data</t>
         </is>
       </c>
-      <c r="C33" s="128" t="inlineStr">
+      <c r="C33" s="134" t="inlineStr">
         <is>
           <t>Rows already filled are DEMO data. Clear only the cream input cells (or run ClearDemoData macro) before going live.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="B34" s="127" t="inlineStr">
+      <c r="B34" s="133" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="C34" s="128" t="inlineStr">
+      <c r="C34" s="134" t="inlineStr">
         <is>
           <t>20,000 lines per register per year. At year end: Save As a new file, set new FY start, carry forward closing stock as Opening Qty/Rate and party balances as Opening Bal.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="B35" s="127" t="inlineStr">
+      <c r="B35" s="133" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="C35" s="128" t="inlineStr">
+      <c r="C35" s="134" t="inlineStr">
         <is>
           <t>Sales return: Adjustments with +qty, reason 'Sales Return', plus a Payment / credit in CashBook. Purchase return: −qty and a Receipt from supplier.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="B36" s="127" t="inlineStr">
+      <c r="B36" s="133" t="inlineStr">
         <is>
           <t>Costing method</t>
         </is>
       </c>
-      <c r="C36" s="128" t="inlineStr">
+      <c r="C36" s="134" t="inlineStr">
         <is>
           <t>Weighted-average cost over the year (opening + all purchases). COGS uses the current average, the standard method for traders.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="B37" s="127" t="inlineStr">
+      <c r="B37" s="133" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C37" s="128" t="inlineStr">
+      <c r="C37" s="134" t="inlineStr">
         <is>
           <t>Currency ₹ and Indian GST structure. Rates in Settings are editable; verify slabs with your CA.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="126" t="inlineStr">
+      <c r="B39" s="132" t="inlineStr">
         <is>
           <t>C ENGINE EDITION (SmartTrader64.xll)</t>
         </is>
@@ -4159,84 +4307,84 @@
       <c r="C39" s="57" t="n"/>
     </row>
     <row r="40" ht="28" customHeight="1">
-      <c r="B40" s="127" t="inlineStr">
+      <c r="B40" s="133" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="C40" s="128" t="inlineStr">
+      <c r="C40" s="134" t="inlineStr">
         <is>
           <t>A native Excel add-in written in C. Stock, cost, GST, party ledgers and the cash book are posted in one pass by compiled code - six formulas instead of ~100,000. Results are identical to the formula edition, cell for cell.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="B41" s="127" t="inlineStr">
+      <c r="B41" s="133" t="inlineStr">
         <is>
           <t>Install once</t>
         </is>
       </c>
-      <c r="C41" s="128" t="inlineStr">
+      <c r="C41" s="134" t="inlineStr">
         <is>
           <t>1) Copy SmartTrader64.xll (or SmartTrader32.xll for 32-bit Office) to a folder, e.g. Documents\SmartTrader. 2) Right-click it &gt; Properties &gt; tick 'Unblock' &gt; OK (Windows blocks add-ins downloaded from the internet). 3) Excel &gt; File &gt; Options &gt; Add-ins &gt; Manage: Excel Add-ins &gt; Go &gt; Browse &gt; pick the .xll &gt; OK.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="B42" s="127" t="inlineStr">
+      <c r="B42" s="133" t="inlineStr">
         <is>
           <t>Check it works</t>
         </is>
       </c>
-      <c r="C42" s="128" t="inlineStr">
+      <c r="C42" s="134" t="inlineStr">
         <is>
           <t>Dashboard top-right shows 'Engine: SmartTrader C Engine 1.0'. A red '!! C engine not loaded' means step 3 was skipped and the grey columns show NAME errors until the add-in is loaded. Your typed data is never affected.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="B43" s="127" t="inlineStr">
+      <c r="B43" s="133" t="inlineStr">
         <is>
           <t>Which .xll?</t>
         </is>
       </c>
-      <c r="C43" s="128" t="inlineStr">
+      <c r="C43" s="134" t="inlineStr">
         <is>
           <t>Excel &gt; File &gt; Account &gt; About Excel shows '64-bit' or '32-bit'. Use the matching file.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="B44" s="127" t="inlineStr">
+      <c r="B44" s="133" t="inlineStr">
         <is>
           <t>Capacity</t>
         </is>
       </c>
-      <c r="C44" s="128" t="inlineStr">
+      <c r="C44" s="134" t="inlineStr">
         <is>
           <t>20,000 lines per register, 2,000 items, 1,000 parties. A full recalculation of the sample data takes about 5 ms.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="B45" s="127" t="inlineStr">
+      <c r="B45" s="133" t="inlineStr">
         <is>
           <t>Do not</t>
         </is>
       </c>
-      <c r="C45" s="128" t="inlineStr">
+      <c r="C45" s="134" t="inlineStr">
         <is>
           <t>Sort the register sheets (the grey output blocks are single array formulas; use the filter arrows instead) or type inside grey columns.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="B46" s="127" t="inlineStr">
+      <c r="B46" s="133" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="C46" s="128" t="inlineStr">
+      <c r="C46" s="134" t="inlineStr">
         <is>
           <t>Excel for Windows (2010 and later, 32- or 64-bit). On Mac / Excel Online use the formula edition (SmartTrader_ERP.xlsx), which has the same layout.</t>
         </is>

--- a/excel/SmartTrader_ERP_C.xlsx
+++ b/excel/SmartTrader_ERP_C.xlsx
@@ -3740,7 +3740,7 @@
     <row r="24">
       <c r="B24" s="70" t="inlineStr">
         <is>
-          <t>1.  Pay for a plan and send your mobile number:  WhatsApp: +91-XXXXXXXXXX  ·  UPI: yourname@upi</t>
+          <t>1.  Buy online at  docbrisk.com/smarttrader  (key appears instantly after payment)</t>
         </is>
       </c>
     </row>

--- a/excel/SmartTrader_ERP_C.xlsx
+++ b/excel/SmartTrader_ERP_C.xlsx
@@ -4472,7 +4472,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <f>SUMPRODUCT(CODE(MID(A5,ROW($A$1:$A$40),1))*(MOD(ROW($A$1:$A$40)*7919,10007)+1))</f>
+        <f>SUMPRODUCT(CODE(MID(A5,ROW($A$1:$A$40),1))*(MOD(ROW($A$1:$A$40)*4517,9973)+1))</f>
         <v/>
       </c>
       <c r="B6" t="inlineStr">
@@ -4483,7 +4483,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <f>MOD(A6*9967+424242,1679616)</f>
+        <f>MOD(A6*8803+615290,1679616)</f>
         <v/>
       </c>
       <c r="B7" t="inlineStr">
